--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1004,53 +1004,53 @@
     <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
+</t>
+  </si>
+  <si>
+    <t>Produit de santé</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.realmCode</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.displayable</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.root</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.extension</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.templateId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeCode</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
+  </si>
+  <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Produit de santé</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.realmCode</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.displayable</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.root</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.extension</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.templateId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeCode</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
